--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5154" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1370,118 +1370,13 @@
     <t>Type de participation</t>
   </si>
   <si>
-    <t>Encounter.participant:responsibleParty.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding.system</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A13-HL7ParticipationType/FHIR/TRE-A13-HL7ParticipationType</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding.code</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.code</t>
-  </si>
-  <si>
-    <t>DIS</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.participant:responsibleParty.type.text</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_A13-HL7ParticipationType/FHIR/TRE-A13-HL7ParticipationType"/&gt;
+    &lt;code value="DIS"/&gt;
+    &lt;display value="Responsable de la sortie"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Encounter.participant:responsibleParty.period</t>
@@ -1963,42 +1858,6 @@
   </si>
   <si>
     <t>PV1-36</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.id</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.extension</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding.system</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.250.1.213.2.14</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding.code</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.hospitalization.dischargeDisposition.text</t>
   </si>
   <si>
     <t>Encounter.location</t>
@@ -2431,11 +2290,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN143"/>
+  <dimension ref="A1:AN121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.26953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="54.26953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.34765625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.46484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -10098,7 +9957,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>79</v>
@@ -10133,7 +9992,7 @@
         <v>80</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>80</v>
@@ -10201,10 +10060,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10227,13 +10086,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>103</v>
+        <v>418</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>104</v>
+        <v>419</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10284,7 +10143,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10296,19 +10155,19 @@
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>106</v>
+        <v>420</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
     </row>
     <row r="70">
@@ -10316,18 +10175,18 @@
         <v>440</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>80</v>
@@ -10336,20 +10195,18 @@
         <v>80</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>109</v>
+        <v>441</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>110</v>
+        <v>442</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10386,53 +10243,55 @@
         <v>80</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>116</v>
+        <v>422</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10453,20 +10312,16 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>146</v>
+        <v>279</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10514,7 +10369,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>448</v>
+        <v>399</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10529,24 +10384,24 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>449</v>
+        <v>404</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>450</v>
+        <v>405</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10655,10 +10510,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>454</v>
+        <v>407</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10728,16 +10583,16 @@
         <v>80</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>116</v>
@@ -10769,45 +10624,45 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>307</v>
+        <v>112</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>308</v>
+        <v>205</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10817,7 +10672,7 @@
         <v>80</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>80</v>
@@ -10856,39 +10711,39 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>310</v>
+        <v>191</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>459</v>
+        <v>409</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10899,7 +10754,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>80</v>
@@ -10911,16 +10766,16 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>313</v>
+        <v>437</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>315</v>
+        <v>412</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10946,13 +10801,11 @@
         <v>80</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10970,13 +10823,13 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>316</v>
+        <v>409</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>80</v>
@@ -10985,24 +10838,24 @@
         <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>80</v>
+        <v>414</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>317</v>
+        <v>415</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>318</v>
+        <v>416</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11022,21 +10875,19 @@
         <v>80</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>168</v>
+        <v>254</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>321</v>
+        <v>419</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
@@ -11045,7 +10896,7 @@
         <v>80</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>462</v>
+        <v>80</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>80</v>
@@ -11084,7 +10935,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>323</v>
+        <v>417</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11102,21 +10953,21 @@
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>324</v>
+        <v>420</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>325</v>
+        <v>421</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11124,7 +10975,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>88</v>
@@ -11139,18 +10990,16 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>441</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>327</v>
+        <v>453</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>328</v>
+        <v>425</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11198,7 +11047,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>330</v>
+        <v>422</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11213,24 +11062,24 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>331</v>
+        <v>427</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>332</v>
+        <v>429</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11241,7 +11090,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -11253,20 +11102,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>334</v>
+        <v>455</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>335</v>
+        <v>456</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11314,13 +11159,13 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>339</v>
+        <v>454</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
@@ -11329,24 +11174,24 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>340</v>
+        <v>458</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>341</v>
+        <v>459</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11354,7 +11199,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>88</v>
@@ -11366,23 +11211,21 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>80</v>
       </c>
@@ -11430,7 +11273,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11445,24 +11288,24 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>417</v>
+        <v>468</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11485,15 +11328,17 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>254</v>
+        <v>469</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>418</v>
+        <v>470</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11542,7 +11387,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>417</v>
+        <v>468</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11557,35 +11402,35 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>80</v>
+        <v>464</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>421</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>80</v>
+        <v>476</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>80</v>
@@ -11597,15 +11442,17 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -11630,13 +11477,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -11654,13 +11501,13 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>80</v>
@@ -11669,30 +11516,28 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>426</v>
+        <v>482</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>427</v>
+        <v>483</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>429</v>
+        <v>485</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>80</v>
+        <v>476</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11711,15 +11556,17 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>279</v>
+        <v>487</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -11768,7 +11615,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>399</v>
+        <v>486</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11783,24 +11630,24 @@
         <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>403</v>
+        <v>482</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>404</v>
+        <v>483</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>405</v>
+        <v>485</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>406</v>
+        <v>489</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11811,7 +11658,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -11820,16 +11667,16 @@
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>103</v>
+        <v>490</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>104</v>
+        <v>491</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11880,25 +11727,25 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>105</v>
+        <v>489</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>106</v>
+        <v>492</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -11909,21 +11756,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>407</v>
+        <v>493</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11935,17 +11782,15 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11994,19 +11839,19 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
@@ -12023,14 +11868,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>408</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12043,26 +11888,24 @@
         <v>80</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O85" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12110,7 +11953,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12128,7 +11971,7 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
@@ -12139,14 +11982,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>409</v>
+        <v>495</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12159,24 +12002,26 @@
         <v>80</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>437</v>
+        <v>287</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>411</v>
+        <v>288</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12200,11 +12045,13 @@
         <v>80</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>487</v>
+        <v>80</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -12222,7 +12069,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>409</v>
+        <v>289</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12234,35 +12081,35 @@
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>415</v>
+        <v>191</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>416</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>417</v>
+        <v>496</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>80</v>
+        <v>497</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>88</v>
@@ -12274,18 +12121,20 @@
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>254</v>
+        <v>498</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>418</v>
+        <v>499</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12334,10 +12183,10 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>417</v>
+        <v>496</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>88</v>
@@ -12349,24 +12198,24 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>80</v>
+        <v>501</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>420</v>
+        <v>502</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>80</v>
+        <v>484</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>421</v>
+        <v>503</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12374,7 +12223,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>88</v>
@@ -12386,16 +12235,16 @@
         <v>80</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>478</v>
+        <v>228</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>425</v>
+        <v>506</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12422,13 +12271,13 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>80</v>
+        <v>507</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>80</v>
+        <v>508</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12446,7 +12295,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12461,24 +12310,24 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>426</v>
+        <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>427</v>
+        <v>106</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>428</v>
+        <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12489,7 +12338,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -12498,16 +12347,16 @@
         <v>80</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12558,13 +12407,13 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>80</v>
@@ -12573,24 +12422,24 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>496</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12598,7 +12447,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>88</v>
@@ -12613,16 +12462,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>254</v>
+        <v>515</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12672,13 +12521,13 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>80</v>
@@ -12687,24 +12536,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>503</v>
+        <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>504</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12727,16 +12576,16 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>506</v>
+        <v>279</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12786,7 +12635,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12801,35 +12650,35 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>511</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>80</v>
@@ -12838,20 +12687,18 @@
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>514</v>
+        <v>103</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -12876,13 +12723,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>518</v>
+        <v>80</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -12900,43 +12747,43 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>512</v>
+        <v>105</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>519</v>
+        <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>520</v>
+        <v>106</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>513</v>
+        <v>108</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12952,19 +12799,19 @@
         <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>524</v>
+        <v>109</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>525</v>
+        <v>110</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>515</v>
+        <v>111</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>516</v>
+        <v>112</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13014,7 +12861,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>523</v>
+        <v>116</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13026,31 +12873,31 @@
         <v>80</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>519</v>
+        <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>520</v>
+        <v>106</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13063,22 +12910,26 @@
         <v>80</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>527</v>
+        <v>287</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
       </c>
@@ -13126,7 +12977,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>526</v>
+        <v>289</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13138,13 +12989,13 @@
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>529</v>
+        <v>191</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>80</v>
@@ -13155,10 +13006,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13181,13 +13032,13 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>103</v>
+        <v>529</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>104</v>
+        <v>530</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13238,7 +13089,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>105</v>
+        <v>528</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13250,38 +13101,38 @@
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>80</v>
+        <v>531</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>80</v>
@@ -13293,17 +13144,15 @@
         <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13352,19 +13201,19 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>80</v>
@@ -13381,14 +13230,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13401,26 +13250,24 @@
         <v>80</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>288</v>
+        <v>111</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O97" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>80</v>
       </c>
@@ -13456,19 +13303,19 @@
         <v>80</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13486,7 +13333,7 @@
         <v>80</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>80</v>
@@ -13497,18 +13344,18 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>534</v>
+        <v>80</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>88</v>
@@ -13517,24 +13364,26 @@
         <v>80</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>535</v>
+        <v>168</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>536</v>
+        <v>218</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>537</v>
+        <v>219</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
       </c>
@@ -13558,13 +13407,13 @@
         <v>80</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>80</v>
+        <v>222</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>80</v>
@@ -13582,10 +13431,10 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>533</v>
+        <v>225</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>88</v>
@@ -13597,24 +13446,24 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>538</v>
+        <v>80</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>539</v>
+        <v>226</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>540</v>
+        <v>191</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13622,7 +13471,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>88</v>
@@ -13634,19 +13483,23 @@
         <v>80</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>228</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>542</v>
+        <v>229</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>80</v>
       </c>
@@ -13670,13 +13523,11 @@
         <v>80</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>545</v>
+        <v>233</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>80</v>
@@ -13694,7 +13545,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>541</v>
+        <v>234</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13712,21 +13563,21 @@
         <v>80</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>80</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13734,7 +13585,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>88</v>
@@ -13746,31 +13597,35 @@
         <v>80</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>547</v>
+        <v>130</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>548</v>
+        <v>237</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>80</v>
+        <v>539</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>80</v>
+        <v>241</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>80</v>
@@ -13806,7 +13661,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>546</v>
+        <v>242</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13824,21 +13679,21 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>550</v>
+        <v>243</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>80</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13846,7 +13701,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>88</v>
@@ -13858,19 +13713,19 @@
         <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>552</v>
+        <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>553</v>
+        <v>246</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>554</v>
+        <v>247</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>555</v>
+        <v>248</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13884,7 +13739,7 @@
         <v>80</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>80</v>
@@ -13920,13 +13775,13 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>551</v>
+        <v>250</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>80</v>
@@ -13938,21 +13793,21 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>556</v>
+        <v>251</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13972,20 +13827,18 @@
         <v>80</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>558</v>
+        <v>255</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14034,7 +13887,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>557</v>
+        <v>257</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14052,21 +13905,21 @@
         <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>561</v>
+        <v>258</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14086,18 +13939,20 @@
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>102</v>
+        <v>261</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>103</v>
+        <v>262</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14146,7 +14001,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>105</v>
+        <v>265</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14158,38 +14013,38 @@
         <v>80</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>106</v>
+        <v>266</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>80</v>
@@ -14201,17 +14056,15 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>109</v>
+        <v>544</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>110</v>
+        <v>545</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14260,25 +14113,25 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>116</v>
+        <v>543</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>106</v>
+        <v>547</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>80</v>
@@ -14289,46 +14142,42 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>286</v>
+        <v>80</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>109</v>
+        <v>228</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>287</v>
+        <v>549</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>80</v>
       </c>
@@ -14352,13 +14201,13 @@
         <v>80</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>80</v>
+        <v>551</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>80</v>
+        <v>552</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>80</v>
@@ -14376,39 +14225,39 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>289</v>
+        <v>548</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>191</v>
+        <v>553</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>80</v>
+        <v>554</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14431,13 +14280,13 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14464,13 +14313,13 @@
         <v>80</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>80</v>
+        <v>559</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>80</v>
@@ -14488,7 +14337,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14506,21 +14355,21 @@
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14531,7 +14380,7 @@
         <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>80</v>
@@ -14543,16 +14392,20 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>103</v>
+        <v>562</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
       </c>
@@ -14576,13 +14429,13 @@
         <v>80</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>80</v>
+        <v>566</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>80</v>
+        <v>567</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>80</v>
@@ -14600,31 +14453,31 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>105</v>
+        <v>561</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>106</v>
+        <v>568</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>80</v>
+        <v>569</v>
       </c>
     </row>
     <row r="108">
@@ -14636,7 +14489,7 @@
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -14655,17 +14508,15 @@
         <v>80</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>109</v>
+        <v>228</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>110</v>
+        <v>571</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>80</v>
@@ -14690,31 +14541,31 @@
         <v>80</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>80</v>
+        <v>573</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>80</v>
+        <v>574</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>116</v>
+        <v>570</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14726,27 +14577,27 @@
         <v>80</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>106</v>
+        <v>575</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>80</v>
+        <v>576</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14757,32 +14608,28 @@
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>218</v>
+        <v>578</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
       </c>
@@ -14806,13 +14653,13 @@
         <v>80</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>223</v>
+        <v>580</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>224</v>
+        <v>581</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>80</v>
@@ -14830,13 +14677,13 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>225</v>
+        <v>577</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>80</v>
@@ -14848,21 +14695,21 @@
         <v>80</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>226</v>
+        <v>582</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>191</v>
+        <v>583</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14870,7 +14717,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>88</v>
@@ -14882,23 +14729,19 @@
         <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>228</v>
+        <v>544</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>229</v>
+        <v>585</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>80</v>
       </c>
@@ -14922,11 +14765,13 @@
         <v>80</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y110" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z110" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>80</v>
@@ -14944,7 +14789,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>234</v>
+        <v>584</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14962,21 +14807,21 @@
         <v>80</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>226</v>
+        <v>587</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>235</v>
+        <v>588</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14984,7 +14829,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>88</v>
@@ -14996,35 +14841,31 @@
         <v>80</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>130</v>
+        <v>228</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>237</v>
+        <v>590</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>80</v>
@@ -15036,13 +14877,11 @@
         <v>80</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>80</v>
+        <v>592</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -15060,7 +14899,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>242</v>
+        <v>589</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15078,21 +14917,21 @@
         <v>80</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>243</v>
+        <v>593</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>244</v>
+        <v>594</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15112,19 +14951,19 @@
         <v>80</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>246</v>
+        <v>596</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>247</v>
+        <v>597</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>248</v>
+        <v>598</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15138,7 +14977,7 @@
         <v>80</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>80</v>
@@ -15174,13 +15013,13 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>250</v>
+        <v>595</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>80</v>
@@ -15192,21 +15031,21 @@
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>251</v>
+        <v>599</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15226,16 +15065,16 @@
         <v>80</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>255</v>
+        <v>103</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>256</v>
+        <v>104</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15286,7 +15125,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>257</v>
+        <v>105</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15298,38 +15137,38 @@
         <v>80</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>80</v>
@@ -15338,19 +15177,19 @@
         <v>80</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>261</v>
+        <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>263</v>
+        <v>111</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>264</v>
+        <v>112</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15400,71 +15239,75 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>266</v>
+        <v>106</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>267</v>
+        <v>80</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>581</v>
+        <v>109</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>582</v>
+        <v>287</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>80</v>
       </c>
@@ -15512,25 +15355,25 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>580</v>
+        <v>289</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>584</v>
+        <v>191</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>80</v>
@@ -15541,10 +15384,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15552,7 +15395,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>88</v>
@@ -15567,13 +15410,13 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>228</v>
+        <v>604</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15600,13 +15443,13 @@
         <v>80</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>589</v>
+        <v>80</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>80</v>
@@ -15624,10 +15467,10 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>88</v>
@@ -15639,24 +15482,24 @@
         <v>100</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>590</v>
+        <v>427</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>80</v>
+        <v>608</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15679,15 +15522,17 @@
         <v>80</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>593</v>
+        <v>611</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -15712,13 +15557,13 @@
         <v>80</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>80</v>
@@ -15736,7 +15581,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15754,21 +15599,21 @@
         <v>80</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>106</v>
+        <v>616</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>597</v>
+        <v>80</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15779,7 +15624,7 @@
         <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>80</v>
@@ -15794,17 +15639,15 @@
         <v>228</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>599</v>
+        <v>618</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>80</v>
       </c>
@@ -15830,11 +15673,9 @@
       <c r="X118" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Y118" t="s" s="2">
-        <v>603</v>
-      </c>
+      <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>80</v>
@@ -15852,13 +15693,13 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>80</v>
@@ -15870,21 +15711,21 @@
         <v>80</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>605</v>
+        <v>80</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>606</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15895,7 +15736,7 @@
         <v>78</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>80</v>
@@ -15907,13 +15748,13 @@
         <v>80</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15940,13 +15781,13 @@
         <v>80</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>610</v>
+        <v>80</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>611</v>
+        <v>80</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>80</v>
@@ -15964,13 +15805,13 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>80</v>
@@ -15982,21 +15823,21 @@
         <v>80</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>612</v>
+        <v>420</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>613</v>
+        <v>80</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16007,7 +15848,7 @@
         <v>78</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>80</v>
@@ -16019,13 +15860,13 @@
         <v>80</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16052,13 +15893,13 @@
         <v>80</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>617</v>
+        <v>80</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>618</v>
+        <v>80</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>80</v>
@@ -16076,13 +15917,13 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>80</v>
@@ -16091,24 +15932,24 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>620</v>
+        <v>629</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16131,15 +15972,17 @@
         <v>80</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>581</v>
+        <v>631</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>633</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>634</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -16188,7 +16031,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16203,2515 +16046,15 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>80</v>
+        <v>635</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y122" s="2"/>
-      <c r="Z122" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="P133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="P137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y140" s="2"/>
-      <c r="Z140" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN143" t="s" s="2">
         <v>80</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1368,15 +1368,6 @@
   </si>
   <si>
     <t>Type de participation</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_A13-HL7ParticipationType/FHIR/TRE-A13-HL7ParticipationType"/&gt;
-    &lt;code value="DIS"/&gt;
-    &lt;display value="Responsable de la sortie"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Encounter.participant:responsibleParty.period</t>
@@ -9957,7 +9948,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>79</v>
@@ -9992,7 +9983,7 @@
         <v>80</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>80</v>
@@ -10060,7 +10051,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>417</v>
@@ -10172,7 +10163,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>422</v>
@@ -10198,10 +10189,10 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="M70" t="s" s="2">
         <v>425</v>
@@ -10284,13 +10275,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>399</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>80</v>
@@ -10315,7 +10306,7 @@
         <v>279</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>401</v>
@@ -10398,7 +10389,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>406</v>
@@ -10510,7 +10501,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>407</v>
@@ -10624,7 +10615,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>408</v>
@@ -10740,7 +10731,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>409</v>
@@ -10805,7 +10796,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10852,7 +10843,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>417</v>
@@ -10964,7 +10955,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>422</v>
@@ -10990,10 +10981,10 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>425</v>
@@ -11076,10 +11067,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11102,13 +11093,13 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11159,7 +11150,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11177,21 +11168,21 @@
         <v>397</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>459</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11217,13 +11208,13 @@
         <v>254</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11273,7 +11264,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11288,24 +11279,24 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL79" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AL79" t="s" s="2">
+      <c r="AM79" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11328,16 +11319,16 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11387,7 +11378,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11402,28 +11393,28 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>474</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11445,13 +11436,13 @@
         <v>228</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11480,11 +11471,11 @@
         <v>172</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>481</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
       </c>
@@ -11501,7 +11492,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11516,28 +11507,28 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AM81" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>485</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11556,16 +11547,16 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L82" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="M82" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11615,7 +11606,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11630,24 +11621,24 @@
         <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AM82" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>485</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11673,10 +11664,10 @@
         <v>279</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11727,7 +11718,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11745,7 +11736,7 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -11756,10 +11747,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11868,10 +11859,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11982,10 +11973,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12098,14 +12089,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12124,16 +12115,16 @@
         <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="N87" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12183,7 +12174,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>88</v>
@@ -12198,24 +12189,24 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="AM87" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12241,10 +12232,10 @@
         <v>228</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12274,11 +12265,11 @@
         <v>172</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
       </c>
@@ -12295,7 +12286,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12324,10 +12315,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12350,13 +12341,13 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12407,7 +12398,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12425,7 +12416,7 @@
         <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
@@ -12436,10 +12427,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12462,16 +12453,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12521,7 +12512,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12539,7 +12530,7 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
@@ -12550,10 +12541,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12579,13 +12570,13 @@
         <v>279</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12635,7 +12626,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12653,7 +12644,7 @@
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
@@ -12664,10 +12655,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12776,10 +12767,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12890,10 +12881,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13006,10 +12997,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13035,10 +13026,10 @@
         <v>208</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13089,7 +13080,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13113,15 +13104,15 @@
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13230,10 +13221,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13344,10 +13335,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13460,10 +13451,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13492,7 +13483,7 @@
         <v>229</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>231</v>
@@ -13574,10 +13565,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13606,7 +13597,7 @@
         <v>237</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>239</v>
@@ -13619,7 +13610,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>80</v>
@@ -13690,10 +13681,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13804,10 +13795,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13916,10 +13907,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14030,10 +14021,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14056,13 +14047,13 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14113,7 +14104,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14131,7 +14122,7 @@
         <v>80</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>80</v>
@@ -14142,10 +14133,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14171,10 +14162,10 @@
         <v>228</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14204,11 +14195,11 @@
         <v>172</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="Z105" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="AA105" t="s" s="2">
         <v>80</v>
       </c>
@@ -14225,7 +14216,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14243,21 +14234,21 @@
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>554</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14283,10 +14274,10 @@
         <v>228</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14316,11 +14307,11 @@
         <v>158</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="Z106" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="AA106" t="s" s="2">
         <v>80</v>
       </c>
@@ -14337,7 +14328,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14361,15 +14352,15 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14395,16 +14386,16 @@
         <v>228</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -14432,11 +14423,11 @@
         <v>158</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>80</v>
       </c>
@@ -14453,7 +14444,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14471,21 +14462,21 @@
         <v>80</v>
       </c>
       <c r="AL107" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>569</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14511,10 +14502,10 @@
         <v>228</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14544,11 +14535,11 @@
         <v>172</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z108" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="Z108" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="AA108" t="s" s="2">
         <v>80</v>
       </c>
@@ -14565,7 +14556,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14583,21 +14574,21 @@
         <v>80</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>576</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14623,10 +14614,10 @@
         <v>228</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14656,11 +14647,11 @@
         <v>172</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>80</v>
       </c>
@@ -14677,7 +14668,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14695,21 +14686,21 @@
         <v>80</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>583</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14732,13 +14723,13 @@
         <v>80</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14789,7 +14780,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14807,21 +14798,21 @@
         <v>80</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14847,10 +14838,10 @@
         <v>228</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14881,7 +14872,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -14899,7 +14890,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14917,21 +14908,21 @@
         <v>80</v>
       </c>
       <c r="AL111" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>594</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14957,13 +14948,13 @@
         <v>279</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15013,7 +15004,7 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15031,7 +15022,7 @@
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>80</v>
@@ -15042,10 +15033,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15154,10 +15145,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15268,10 +15259,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15384,10 +15375,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15410,13 +15401,13 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15467,7 +15458,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>88</v>
@@ -15482,24 +15473,24 @@
         <v>100</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>427</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>609</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15525,13 +15516,13 @@
         <v>168</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15560,11 +15551,11 @@
         <v>222</v>
       </c>
       <c r="Y117" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="Z117" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="Z117" t="s" s="2">
-        <v>615</v>
-      </c>
       <c r="AA117" t="s" s="2">
         <v>80</v>
       </c>
@@ -15581,7 +15572,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15599,7 +15590,7 @@
         <v>80</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>80</v>
@@ -15610,10 +15601,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15639,13 +15630,13 @@
         <v>228</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15675,7 +15666,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>80</v>
@@ -15693,7 +15684,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15722,10 +15713,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15751,10 +15742,10 @@
         <v>254</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15805,7 +15796,7 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15834,10 +15825,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15863,10 +15854,10 @@
         <v>261</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15917,7 +15908,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15935,21 +15926,21 @@
         <v>426</v>
       </c>
       <c r="AL120" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>629</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15972,16 +15963,16 @@
         <v>80</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16031,7 +16022,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16046,10 +16037,10 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/main/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
